--- a/public/asset/ecommerce_25_male_employees_per_department_with_dob.xlsx
+++ b/public/asset/ecommerce_25_male_employees_per_department_with_dob.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\system\public\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB349FF8-4B05-468B-8E62-BF6F1EBE8A0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D673D43-2CF4-48A7-922D-D69F1EDB3BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10181,6 +10181,7 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -10197,7 +10198,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -10497,6 +10497,7 @@
           <a:lstStyle/>
           <a:p>
             <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Employees by Organization</a:t>
             </a:r>
           </a:p>
@@ -11513,7 +11514,7 @@
       <c r="E2" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="F2" s="17" t="s">
         <v>24</v>
       </c>
       <c r="G2" t="s">
@@ -39613,12 +39614,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>3287</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="5" t="s">
@@ -39950,10 +39951,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>3299</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="19"/>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" s="4" t="s">
@@ -40054,11 +40055,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="17.399999999999999">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="20" t="s">
         <v>3320</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="21"/>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="12" t="s">
@@ -40441,10 +40442,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="17.399999999999999">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="22" t="s">
         <v>3333</v>
       </c>
-      <c r="B1" s="22"/>
+      <c r="B1" s="23"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
